--- a/data/agents.xlsx
+++ b/data/agents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kavya</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -452,7 +452,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>harinee</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>thilak</t>
+          <t>Thilak</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>praveen</t>
+          <t>Praveen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
